--- a/target/test-classes/TestData/LoginData.xlsx
+++ b/target/test-classes/TestData/LoginData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JavaSeleniumAutomation\AutomationFramework\src\test\resources\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152FD3D8-836B-416E-A1F6-D13707CDD3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56639B40-1450-4CEE-9693-B21CB14E60AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{DD9372B6-632C-4358-ABD2-4DD3DF92ABC1}"/>
   </bookViews>
@@ -72,9 +72,6 @@
     <t>wrong_user</t>
   </si>
   <si>
-    <t>UserName and Password Donot Match</t>
-  </si>
-  <si>
     <t>locked_out_user</t>
   </si>
   <si>
@@ -85,6 +82,9 @@
   </si>
   <si>
     <t>Epic sadface: Username is required</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Username and password do not match any user in this service</t>
   </si>
 </sst>
 </file>
@@ -540,7 +540,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -559,18 +559,18 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
